--- a/nablarch_sample_aws/アプリケーション方式設計書_2全体概要_AWS.xlsx
+++ b/nablarch_sample_aws/アプリケーション方式設計書_2全体概要_AWS.xlsx
@@ -3,13 +3,16 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D4BB540-EF7C-4BAF-ACB2-15CC470010D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C32A0103-1C02-4519-AFA3-38A72FE8E32A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1245" yWindow="-120" windowWidth="27675" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2.全体概要" sheetId="13" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'2.全体概要'!$A$1:$AI$94</definedName>
+  </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -782,6 +785,39 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -839,39 +875,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="ハイパーリンク" xfId="4" builtinId="8"/>
@@ -906,13 +909,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>117662</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>49</xdr:row>
       <xdr:rowOff>112059</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
       <xdr:colOff>250975</xdr:colOff>
-      <xdr:row>69</xdr:row>
+      <xdr:row>68</xdr:row>
       <xdr:rowOff>104776</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
@@ -928,7 +931,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="1222562" y="7370109"/>
+          <a:off x="1222562" y="7227234"/>
           <a:ext cx="7591388" cy="2707342"/>
           <a:chOff x="1222562" y="7370109"/>
           <a:chExt cx="7591388" cy="2707342"/>
@@ -5168,10 +5171,10 @@
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="62" name="グループ化 61">
+        <xdr:cNvPr id="4" name="グループ化 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6837A4B4-183E-E72E-9385-7F0514C9ABA7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35305A45-8718-0A3D-2468-732875E3ED77}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5181,8 +5184,8 @@
         <a:xfrm>
           <a:off x="1098079" y="1339077"/>
           <a:ext cx="8300086" cy="4836166"/>
-          <a:chOff x="1097094" y="1356156"/>
-          <a:chExt cx="8289904" cy="4892003"/>
+          <a:chOff x="1098079" y="1339077"/>
+          <a:chExt cx="8300086" cy="4836166"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:sp macro="" textlink="">
@@ -5200,8 +5203,8 @@
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="3224839" y="1445173"/>
-            <a:ext cx="4546248" cy="3511778"/>
+            <a:off x="3228437" y="1427078"/>
+            <a:ext cx="4551832" cy="3471695"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -5352,8 +5355,8 @@
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="5619521" y="4110698"/>
-            <a:ext cx="1846215" cy="778552"/>
+            <a:off x="5626061" y="4062179"/>
+            <a:ext cx="1848483" cy="769666"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -5552,8 +5555,8 @@
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="3442945" y="3481244"/>
-            <a:ext cx="1846215" cy="778552"/>
+            <a:off x="3446811" y="3439909"/>
+            <a:ext cx="1848483" cy="769666"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -5736,8 +5739,8 @@
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="3452459" y="2604607"/>
-            <a:ext cx="1846215" cy="778552"/>
+            <a:off x="3456337" y="2573278"/>
+            <a:ext cx="1848483" cy="769666"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -5936,8 +5939,8 @@
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="3452459" y="1718336"/>
-            <a:ext cx="1846215" cy="778552"/>
+            <a:off x="3456337" y="1697123"/>
+            <a:ext cx="1848483" cy="769666"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -6134,8 +6137,8 @@
         </xdr:nvGrpSpPr>
         <xdr:grpSpPr>
           <a:xfrm>
-            <a:off x="2560493" y="2980647"/>
-            <a:ext cx="296029" cy="701561"/>
+            <a:off x="2563275" y="2945026"/>
+            <a:ext cx="296393" cy="693553"/>
             <a:chOff x="1762125" y="1781175"/>
             <a:chExt cx="295275" cy="1190625"/>
           </a:xfrm>
@@ -6284,8 +6287,8 @@
         </xdr:nvGrpSpPr>
         <xdr:grpSpPr>
           <a:xfrm>
-            <a:off x="2560493" y="2055234"/>
-            <a:ext cx="296029" cy="759555"/>
+            <a:off x="2563275" y="2030176"/>
+            <a:ext cx="296393" cy="750885"/>
             <a:chOff x="1762125" y="1781175"/>
             <a:chExt cx="295275" cy="1190625"/>
           </a:xfrm>
@@ -6436,8 +6439,8 @@
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="8844077" y="1511364"/>
-            <a:ext cx="542921" cy="1729517"/>
+            <a:off x="8854577" y="1492513"/>
+            <a:ext cx="543588" cy="1709776"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -6583,8 +6586,8 @@
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="1097094" y="2621358"/>
-            <a:ext cx="1246076" cy="235748"/>
+            <a:off x="1098079" y="2589838"/>
+            <a:ext cx="1247606" cy="233057"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -6736,8 +6739,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="3644692" y="2057890"/>
-            <a:ext cx="1502669" cy="325619"/>
+            <a:off x="3648806" y="2032801"/>
+            <a:ext cx="1504515" cy="321902"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -6896,8 +6899,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="3641203" y="2958234"/>
-            <a:ext cx="1506157" cy="325012"/>
+            <a:off x="3645313" y="2922869"/>
+            <a:ext cx="1508007" cy="321302"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -7061,8 +7064,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="5803617" y="4420379"/>
-            <a:ext cx="1506996" cy="300468"/>
+            <a:off x="5810383" y="4368325"/>
+            <a:ext cx="1508847" cy="297038"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -7205,8 +7208,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="3608013" y="2959290"/>
-            <a:ext cx="1541240" cy="356435"/>
+            <a:off x="3612082" y="2923913"/>
+            <a:ext cx="1543133" cy="352367"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -7350,8 +7353,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="3655581" y="2050003"/>
-            <a:ext cx="1516401" cy="367296"/>
+            <a:off x="3659708" y="2025004"/>
+            <a:ext cx="1518264" cy="363104"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -7499,8 +7502,8 @@
         </xdr:nvCxnSpPr>
         <xdr:spPr>
           <a:xfrm flipV="1">
-            <a:off x="5147360" y="2972014"/>
-            <a:ext cx="826884" cy="148726"/>
+            <a:off x="5153320" y="2936492"/>
+            <a:ext cx="827900" cy="147028"/>
           </a:xfrm>
           <a:prstGeom prst="bentConnector3">
             <a:avLst>
@@ -7546,8 +7549,8 @@
         </xdr:nvCxnSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="5147361" y="2220700"/>
-            <a:ext cx="1326954" cy="243783"/>
+            <a:off x="5153321" y="2193753"/>
+            <a:ext cx="1328584" cy="241000"/>
           </a:xfrm>
           <a:prstGeom prst="bentConnector2">
             <a:avLst/>
@@ -7589,8 +7592,8 @@
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="5330364" y="5856876"/>
-            <a:ext cx="2507808" cy="391283"/>
+            <a:off x="5336548" y="5788426"/>
+            <a:ext cx="2510888" cy="386817"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -7736,8 +7739,8 @@
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="4971454" y="5352850"/>
-            <a:ext cx="1290431" cy="356121"/>
+            <a:off x="4977198" y="5290153"/>
+            <a:ext cx="1292016" cy="352056"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -7899,8 +7902,8 @@
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="6761847" y="5372675"/>
-            <a:ext cx="1422342" cy="339944"/>
+            <a:off x="6769790" y="5309752"/>
+            <a:ext cx="1424089" cy="336064"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -8062,8 +8065,8 @@
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="2047011" y="1356156"/>
-            <a:ext cx="1225623" cy="454155"/>
+            <a:off x="2049163" y="1339077"/>
+            <a:ext cx="1227128" cy="448971"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -8234,8 +8237,8 @@
         </xdr:nvCxnSpPr>
         <xdr:spPr>
           <a:xfrm flipV="1">
-            <a:off x="1943621" y="2233651"/>
-            <a:ext cx="1711960" cy="183508"/>
+            <a:off x="1945646" y="2206556"/>
+            <a:ext cx="1714063" cy="181413"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -8278,8 +8281,8 @@
         </xdr:nvCxnSpPr>
         <xdr:spPr>
           <a:xfrm flipV="1">
-            <a:off x="1924279" y="3137508"/>
-            <a:ext cx="1683734" cy="326647"/>
+            <a:off x="1926280" y="3100097"/>
+            <a:ext cx="1685802" cy="322919"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -8319,8 +8322,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="2347077" y="2529481"/>
-            <a:ext cx="774495" cy="171559"/>
+            <a:off x="2349597" y="2499010"/>
+            <a:ext cx="775446" cy="169601"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -8377,8 +8380,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="2398709" y="3440184"/>
-            <a:ext cx="619597" cy="143989"/>
+            <a:off x="2401293" y="3399318"/>
+            <a:ext cx="620358" cy="142346"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -8437,8 +8440,8 @@
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="1163363" y="3750829"/>
-            <a:ext cx="1345901" cy="228978"/>
+            <a:off x="1164429" y="3706417"/>
+            <a:ext cx="1347554" cy="226364"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -8590,8 +8593,8 @@
         </xdr:nvGrpSpPr>
         <xdr:grpSpPr>
           <a:xfrm>
-            <a:off x="8316785" y="1641004"/>
-            <a:ext cx="296029" cy="701561"/>
+            <a:off x="8326638" y="1620674"/>
+            <a:ext cx="296393" cy="693553"/>
             <a:chOff x="1762125" y="1781175"/>
             <a:chExt cx="295275" cy="1190625"/>
           </a:xfrm>
@@ -8740,8 +8743,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="8155002" y="2125891"/>
-            <a:ext cx="636807" cy="143990"/>
+            <a:off x="8164656" y="2100026"/>
+            <a:ext cx="637589" cy="142347"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -8798,8 +8801,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="5393120" y="1822019"/>
-            <a:ext cx="3379381" cy="221986"/>
+            <a:off x="5399382" y="1799623"/>
+            <a:ext cx="3383532" cy="219452"/>
           </a:xfrm>
           <a:prstGeom prst="rightArrow">
             <a:avLst/>
@@ -8949,8 +8952,8 @@
         </xdr:nvGrpSpPr>
         <xdr:grpSpPr>
           <a:xfrm rot="16200000">
-            <a:off x="6392658" y="4615800"/>
-            <a:ext cx="278786" cy="1397536"/>
+            <a:off x="6401909" y="4552682"/>
+            <a:ext cx="275604" cy="1399253"/>
             <a:chOff x="1762125" y="1781175"/>
             <a:chExt cx="295275" cy="1190625"/>
           </a:xfrm>
@@ -9099,8 +9102,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="6229350" y="5390891"/>
-            <a:ext cx="619597" cy="143988"/>
+            <a:off x="6236639" y="5327760"/>
+            <a:ext cx="620358" cy="142345"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -9157,8 +9160,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm rot="5400000">
-            <a:off x="5659583" y="5199524"/>
-            <a:ext cx="1006928" cy="172216"/>
+            <a:off x="5672537" y="5137488"/>
+            <a:ext cx="995435" cy="172428"/>
           </a:xfrm>
           <a:prstGeom prst="rightArrow">
             <a:avLst/>
@@ -9312,8 +9315,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm rot="16200000">
-            <a:off x="6395258" y="5175570"/>
-            <a:ext cx="1010675" cy="188588"/>
+            <a:off x="6409139" y="5113704"/>
+            <a:ext cx="999139" cy="188820"/>
           </a:xfrm>
           <a:prstGeom prst="rightArrow">
             <a:avLst/>
@@ -9482,8 +9485,8 @@
         </xdr:blipFill>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="1390349" y="3193659"/>
-            <a:ext cx="533930" cy="540992"/>
+            <a:off x="1391694" y="3155607"/>
+            <a:ext cx="534586" cy="534817"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -9528,8 +9531,8 @@
         </xdr:blipFill>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="1409691" y="2142039"/>
-            <a:ext cx="533930" cy="550239"/>
+            <a:off x="1411060" y="2115990"/>
+            <a:ext cx="534586" cy="543959"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -9561,8 +9564,8 @@
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="1349432" y="4442831"/>
-            <a:ext cx="542921" cy="1679546"/>
+            <a:off x="1350727" y="4390521"/>
+            <a:ext cx="543588" cy="1660376"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -9706,8 +9709,8 @@
         </xdr:nvGrpSpPr>
         <xdr:grpSpPr>
           <a:xfrm>
-            <a:off x="2561768" y="4623093"/>
-            <a:ext cx="296029" cy="701561"/>
+            <a:off x="2564552" y="4568725"/>
+            <a:ext cx="296393" cy="693553"/>
             <a:chOff x="1762125" y="1781175"/>
             <a:chExt cx="295275" cy="1190625"/>
           </a:xfrm>
@@ -9856,8 +9859,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="2399985" y="5113456"/>
-            <a:ext cx="636807" cy="143989"/>
+            <a:off x="2402570" y="5053491"/>
+            <a:ext cx="637589" cy="142346"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -9914,8 +9917,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm rot="19086508">
-            <a:off x="1756057" y="4699702"/>
-            <a:ext cx="2016058" cy="216541"/>
+            <a:off x="1757851" y="4644460"/>
+            <a:ext cx="2018534" cy="214069"/>
           </a:xfrm>
           <a:prstGeom prst="rightArrow">
             <a:avLst/>
@@ -10067,8 +10070,8 @@
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="1833098" y="4171170"/>
-            <a:ext cx="1498845" cy="461883"/>
+            <a:off x="1834987" y="4121961"/>
+            <a:ext cx="1500686" cy="456611"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -10244,8 +10247,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="3622175" y="3810487"/>
-            <a:ext cx="1506157" cy="331273"/>
+            <a:off x="3626261" y="3765394"/>
+            <a:ext cx="1508007" cy="327492"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -10409,8 +10412,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="3608012" y="3804699"/>
-            <a:ext cx="1529885" cy="352093"/>
+            <a:off x="3612081" y="3759672"/>
+            <a:ext cx="1531764" cy="348074"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -10550,8 +10553,8 @@
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="6191074" y="1610137"/>
-            <a:ext cx="1500748" cy="254282"/>
+            <a:off x="6198316" y="1590159"/>
+            <a:ext cx="1502591" cy="251380"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -10719,8 +10722,8 @@
         </xdr:nvGrpSpPr>
         <xdr:grpSpPr>
           <a:xfrm>
-            <a:off x="5974244" y="2464483"/>
-            <a:ext cx="1000142" cy="1015061"/>
+            <a:off x="5981219" y="2434754"/>
+            <a:ext cx="1001370" cy="1003475"/>
             <a:chOff x="5527554" y="2477621"/>
             <a:chExt cx="1000142" cy="1015061"/>
           </a:xfrm>
@@ -11201,8 +11204,8 @@
         </xdr:nvCxnSpPr>
         <xdr:spPr>
           <a:xfrm rot="5400000" flipH="1" flipV="1">
-            <a:off x="6108245" y="3840341"/>
-            <a:ext cx="1028908" cy="131169"/>
+            <a:off x="6121889" y="3794079"/>
+            <a:ext cx="1017164" cy="131330"/>
           </a:xfrm>
           <a:prstGeom prst="bentConnector3">
             <a:avLst>
@@ -11245,8 +11248,8 @@
         </xdr:nvCxnSpPr>
         <xdr:spPr>
           <a:xfrm flipV="1">
-            <a:off x="5137897" y="3391471"/>
-            <a:ext cx="1083990" cy="589275"/>
+            <a:off x="5143845" y="3351161"/>
+            <a:ext cx="1085321" cy="582549"/>
           </a:xfrm>
           <a:prstGeom prst="bentConnector2">
             <a:avLst/>
@@ -11283,8 +11286,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm rot="20043632">
-            <a:off x="2883978" y="3317001"/>
-            <a:ext cx="4762336" cy="1768148"/>
+            <a:off x="3382459" y="2591740"/>
+            <a:ext cx="4768185" cy="1747966"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -11326,6 +11329,366 @@
                 <a:srgbClr val="FF0000"/>
               </a:solidFill>
             </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="2" name="Rectangle 37">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F8664133-4517-5D76-DEBC-1F09E5507310}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr>
+            <a:spLocks noChangeArrowheads="1"/>
+          </xdr:cNvSpPr>
+        </xdr:nvSpPr>
+        <xdr:spPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="8521202" y="4014257"/>
+            <a:ext cx="444998" cy="1178756"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="accent4"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:txBody>
+          <a:bodyPr vert="eaVert" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" anchor="ctr" anchorCtr="0" compatLnSpc="1">
+            <a:prstTxWarp prst="textNoShape">
+              <a:avLst/>
+            </a:prstTxWarp>
+          </a:bodyPr>
+          <a:lstStyle>
+            <a:defPPr>
+              <a:defRPr lang="ja-JP"/>
+            </a:defPPr>
+            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl1pPr>
+            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl2pPr>
+            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl3pPr>
+            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl4pPr>
+            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl5pPr>
+            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl6pPr>
+            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl7pPr>
+            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl8pPr>
+            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl9pPr>
+          </a:lstStyle>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ja-JP" sz="1000" b="0">
+                <a:solidFill>
+                  <a:schemeClr val="bg1"/>
+                </a:solidFill>
+                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>Amazon SES</a:t>
+            </a:r>
+            <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1000" b="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="3" name="カギ線コネクタ 130">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A80F92ED-E7B0-A0D9-92D2-61E95C91199E}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr>
+            <a:cxnSpLocks/>
+            <a:stCxn id="38" idx="3"/>
+            <a:endCxn id="2" idx="1"/>
+          </xdr:cNvCxnSpPr>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="7319230" y="4516844"/>
+            <a:ext cx="1201972" cy="86791"/>
+          </a:xfrm>
+          <a:prstGeom prst="bentConnector3">
+            <a:avLst>
+              <a:gd name="adj1" fmla="val 50000"/>
+            </a:avLst>
+          </a:prstGeom>
+          <a:ln>
+            <a:tailEnd type="arrow"/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="12" name="Rectangle 37">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E8E6F40-DADC-F2D7-60C0-D120C31291F3}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr>
+            <a:spLocks noChangeArrowheads="1"/>
+          </xdr:cNvSpPr>
+        </xdr:nvSpPr>
+        <xdr:spPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="7211667" y="4196156"/>
+            <a:ext cx="1424089" cy="336063"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent3"/>
+          </a:lnRef>
+          <a:fillRef idx="2">
+            <a:schemeClr val="accent3"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent3"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" anchor="ctr" anchorCtr="0" compatLnSpc="1">
+            <a:prstTxWarp prst="textNoShape">
+              <a:avLst/>
+            </a:prstTxWarp>
+          </a:bodyPr>
+          <a:lstStyle>
+            <a:defPPr>
+              <a:defRPr lang="ja-JP"/>
+            </a:defPPr>
+            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl1pPr>
+            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl2pPr>
+            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl3pPr>
+            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl4pPr>
+            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl5pPr>
+            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl6pPr>
+            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl7pPr>
+            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl8pPr>
+            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl9pPr>
+          </a:lstStyle>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="ja-JP" altLang="en-US" sz="900" b="0">
+                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>メール送信</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ja-JP" sz="900" b="0">
+                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>(SMTP)</a:t>
+            </a:r>
           </a:p>
         </xdr:txBody>
       </xdr:sp>
@@ -11659,7 +12022,7 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AI425"/>
+  <dimension ref="A1:AI424"/>
   <sheetFormatPr defaultColWidth="3.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="16384" width="3.625" style="15"/>
@@ -11672,45 +12035,45 @@
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="3"/>
-      <c r="E1" s="38" t="s">
+      <c r="E1" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
-      <c r="M1" s="39"/>
-      <c r="N1" s="39"/>
-      <c r="O1" s="40"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="50"/>
+      <c r="M1" s="50"/>
+      <c r="N1" s="50"/>
+      <c r="O1" s="51"/>
       <c r="P1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="Q1" s="2"/>
-      <c r="R1" s="41" t="s">
+      <c r="R1" s="52" t="s">
         <v>3</v>
       </c>
-      <c r="S1" s="42"/>
-      <c r="T1" s="42"/>
-      <c r="U1" s="42"/>
-      <c r="V1" s="42"/>
-      <c r="W1" s="42"/>
-      <c r="X1" s="43"/>
+      <c r="S1" s="53"/>
+      <c r="T1" s="53"/>
+      <c r="U1" s="53"/>
+      <c r="V1" s="53"/>
+      <c r="W1" s="53"/>
+      <c r="X1" s="54"/>
       <c r="Y1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="Z1" s="3"/>
-      <c r="AA1" s="44"/>
-      <c r="AB1" s="45"/>
-      <c r="AC1" s="45"/>
-      <c r="AD1" s="45"/>
-      <c r="AE1" s="46"/>
-      <c r="AF1" s="35"/>
-      <c r="AG1" s="36"/>
-      <c r="AH1" s="36"/>
-      <c r="AI1" s="37"/>
+      <c r="AA1" s="55"/>
+      <c r="AB1" s="56"/>
+      <c r="AC1" s="56"/>
+      <c r="AD1" s="56"/>
+      <c r="AE1" s="57"/>
+      <c r="AF1" s="46"/>
+      <c r="AG1" s="47"/>
+      <c r="AH1" s="47"/>
+      <c r="AI1" s="48"/>
     </row>
     <row r="2" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
@@ -11719,43 +12082,43 @@
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
       <c r="D2" s="6"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="39"/>
-      <c r="K2" s="39"/>
-      <c r="L2" s="39"/>
-      <c r="M2" s="39"/>
-      <c r="N2" s="39"/>
-      <c r="O2" s="40"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="50"/>
+      <c r="K2" s="50"/>
+      <c r="L2" s="50"/>
+      <c r="M2" s="50"/>
+      <c r="N2" s="50"/>
+      <c r="O2" s="51"/>
       <c r="P2" s="7" t="s">
         <v>6</v>
       </c>
       <c r="Q2" s="8"/>
-      <c r="R2" s="47" t="s">
+      <c r="R2" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="S2" s="48"/>
-      <c r="T2" s="48"/>
-      <c r="U2" s="48"/>
-      <c r="V2" s="48"/>
-      <c r="W2" s="48"/>
-      <c r="X2" s="49"/>
+      <c r="S2" s="59"/>
+      <c r="T2" s="59"/>
+      <c r="U2" s="59"/>
+      <c r="V2" s="59"/>
+      <c r="W2" s="59"/>
+      <c r="X2" s="60"/>
       <c r="Y2" s="1" t="s">
         <v>8</v>
       </c>
       <c r="Z2" s="3"/>
-      <c r="AA2" s="44"/>
-      <c r="AB2" s="45"/>
-      <c r="AC2" s="45"/>
-      <c r="AD2" s="45"/>
-      <c r="AE2" s="46"/>
-      <c r="AF2" s="35"/>
-      <c r="AG2" s="36"/>
-      <c r="AH2" s="36"/>
-      <c r="AI2" s="37"/>
+      <c r="AA2" s="55"/>
+      <c r="AB2" s="56"/>
+      <c r="AC2" s="56"/>
+      <c r="AD2" s="56"/>
+      <c r="AE2" s="57"/>
+      <c r="AF2" s="46"/>
+      <c r="AG2" s="47"/>
+      <c r="AH2" s="47"/>
+      <c r="AI2" s="48"/>
     </row>
     <row r="3" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
@@ -11764,39 +12127,39 @@
       <c r="B3" s="9"/>
       <c r="C3" s="10"/>
       <c r="D3" s="3"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="53"/>
-      <c r="I3" s="53"/>
-      <c r="J3" s="53"/>
-      <c r="K3" s="53"/>
-      <c r="L3" s="53"/>
-      <c r="M3" s="53"/>
-      <c r="N3" s="53"/>
-      <c r="O3" s="53"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="64"/>
+      <c r="K3" s="64"/>
+      <c r="L3" s="64"/>
+      <c r="M3" s="64"/>
+      <c r="N3" s="64"/>
+      <c r="O3" s="64"/>
       <c r="P3" s="11"/>
       <c r="Q3" s="12"/>
-      <c r="R3" s="50"/>
-      <c r="S3" s="51"/>
-      <c r="T3" s="51"/>
-      <c r="U3" s="51"/>
-      <c r="V3" s="51"/>
-      <c r="W3" s="51"/>
-      <c r="X3" s="52"/>
+      <c r="R3" s="61"/>
+      <c r="S3" s="62"/>
+      <c r="T3" s="62"/>
+      <c r="U3" s="62"/>
+      <c r="V3" s="62"/>
+      <c r="W3" s="62"/>
+      <c r="X3" s="63"/>
       <c r="Y3" s="11" t="s">
         <v>10</v>
       </c>
       <c r="Z3" s="13"/>
-      <c r="AA3" s="44"/>
-      <c r="AB3" s="45"/>
-      <c r="AC3" s="45"/>
-      <c r="AD3" s="45"/>
-      <c r="AE3" s="46"/>
-      <c r="AF3" s="35"/>
-      <c r="AG3" s="36"/>
-      <c r="AH3" s="36"/>
-      <c r="AI3" s="37"/>
+      <c r="AA3" s="55"/>
+      <c r="AB3" s="56"/>
+      <c r="AC3" s="56"/>
+      <c r="AD3" s="56"/>
+      <c r="AE3" s="57"/>
+      <c r="AF3" s="46"/>
+      <c r="AG3" s="47"/>
+      <c r="AH3" s="47"/>
+      <c r="AI3" s="48"/>
     </row>
     <row r="4" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="5" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -11875,110 +12238,151 @@
     <row r="41" spans="2:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="42" spans="2:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="43" spans="2:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="44" spans="2:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="45" spans="2:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D45" s="15" t="s">
+    <row r="44" spans="2:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D44" s="15" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="46" spans="2:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D46" s="15" t="s">
+    <row r="45" spans="2:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D45" s="15" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="47" spans="2:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="48" spans="2:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C48" s="14" t="str">
+    <row r="46" spans="2:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="47" spans="2:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C47" s="14" t="str">
         <f>$B$5&amp;"2."</f>
         <v>2.2.</v>
       </c>
-      <c r="D48" s="15" t="s">
+      <c r="D47" s="15" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="49" spans="4:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D49" s="15" t="s">
+    <row r="48" spans="2:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D48" s="15" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="50" spans="4:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="51" spans="4:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="52" spans="4:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="53" spans="4:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="54" spans="4:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="55" spans="4:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="56" spans="4:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="57" spans="4:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="58" spans="4:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="59" spans="4:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="60" spans="4:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="61" spans="4:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="62" spans="4:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="63" spans="4:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="64" spans="4:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="65" spans="3:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="66" spans="3:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="67" spans="3:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="68" spans="3:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="69" spans="3:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="70" spans="3:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="71" spans="3:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="72" spans="3:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D72" s="15" t="s">
+    <row r="49" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="50" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="51" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="52" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="53" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="54" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="55" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="56" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="57" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="58" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="59" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="60" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="61" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="62" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="63" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="64" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="65" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="66" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="67" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="68" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="69" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="70" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="71" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D71" s="15" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="73" spans="3:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D73" s="15" t="s">
+    <row r="72" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D72" s="15" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="74" spans="3:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D74" s="15" t="s">
+    <row r="73" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D73" s="15" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="75" spans="3:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="76" spans="3:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C76" s="14" t="str">
+    <row r="74" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="75" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C75" s="14" t="str">
         <f>$B$5&amp;"3."</f>
         <v>2.3.</v>
       </c>
-      <c r="D76" s="15" t="s">
+      <c r="D75" s="15" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="77" spans="3:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C77" s="14"/>
-      <c r="D77" s="15" t="s">
+    <row r="76" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C76" s="14"/>
+      <c r="D76" s="15" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="78" spans="3:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D78" s="15" t="s">
+    <row r="77" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D77" s="15" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="79" spans="3:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D79" s="16" t="s">
+    <row r="78" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D78" s="16" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="80" spans="3:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C80" s="14"/>
-      <c r="D80" s="14"/>
+    <row r="79" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C79" s="14"/>
+      <c r="D79" s="14"/>
+    </row>
+    <row r="80" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A80" s="18"/>
+      <c r="B80" s="18"/>
+      <c r="C80" s="17" t="str">
+        <f>$B$5&amp;"4."</f>
+        <v>2.4.</v>
+      </c>
+      <c r="D80" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="E80" s="18"/>
+      <c r="F80" s="18"/>
+      <c r="G80" s="18"/>
+      <c r="H80" s="18"/>
+      <c r="I80" s="18"/>
+      <c r="J80" s="18"/>
+      <c r="K80" s="18"/>
+      <c r="L80" s="18"/>
+      <c r="M80" s="18"/>
+      <c r="N80" s="18"/>
+      <c r="O80" s="18"/>
+      <c r="P80" s="18"/>
+      <c r="Q80" s="18"/>
+      <c r="R80" s="18"/>
+      <c r="S80" s="18"/>
+      <c r="T80" s="18"/>
+      <c r="U80" s="18"/>
+      <c r="V80" s="18"/>
+      <c r="W80" s="18"/>
+      <c r="X80" s="18"/>
+      <c r="Y80" s="18"/>
+      <c r="Z80" s="18"/>
+      <c r="AA80" s="18"/>
+      <c r="AB80" s="18"/>
+      <c r="AC80" s="18"/>
+      <c r="AD80" s="18"/>
+      <c r="AE80" s="18"/>
+      <c r="AF80" s="18"/>
+      <c r="AG80" s="18"/>
+      <c r="AH80" s="18"/>
+      <c r="AI80" s="18"/>
     </row>
     <row r="81" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="18"/>
       <c r="B81" s="18"/>
-      <c r="C81" s="17" t="str">
-        <f>$B$5&amp;"4."</f>
-        <v>2.4.</v>
+      <c r="C81" s="17"/>
+      <c r="D81" s="19" t="str">
+        <f>$C$80&amp;"1."</f>
+        <v>2.4.1.</v>
       </c>
-      <c r="D81" s="18" t="s">
+      <c r="E81" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="E81" s="18"/>
       <c r="F81" s="18"/>
       <c r="G81" s="18"/>
       <c r="H81" s="18"/>
@@ -12014,13 +12418,8 @@
       <c r="A82" s="18"/>
       <c r="B82" s="18"/>
       <c r="C82" s="17"/>
-      <c r="D82" s="19" t="str">
-        <f>$C$81&amp;"1."</f>
-        <v>2.4.1.</v>
-      </c>
-      <c r="E82" s="18" t="s">
-        <v>21</v>
-      </c>
+      <c r="D82" s="19"/>
+      <c r="E82" s="18"/>
       <c r="F82" s="18"/>
       <c r="G82" s="18"/>
       <c r="H82" s="18"/>
@@ -12057,7 +12456,9 @@
       <c r="B83" s="18"/>
       <c r="C83" s="17"/>
       <c r="D83" s="19"/>
-      <c r="E83" s="18"/>
+      <c r="E83" s="18" t="s">
+        <v>22</v>
+      </c>
       <c r="F83" s="18"/>
       <c r="G83" s="18"/>
       <c r="H83" s="18"/>
@@ -12095,7 +12496,7 @@
       <c r="C84" s="17"/>
       <c r="D84" s="19"/>
       <c r="E84" s="18" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F84" s="18"/>
       <c r="G84" s="18"/>
@@ -12133,9 +12534,7 @@
       <c r="B85" s="18"/>
       <c r="C85" s="17"/>
       <c r="D85" s="19"/>
-      <c r="E85" s="18" t="s">
-        <v>23</v>
-      </c>
+      <c r="E85" s="18"/>
       <c r="F85" s="18"/>
       <c r="G85" s="18"/>
       <c r="H85" s="18"/>
@@ -12172,36 +12571,42 @@
       <c r="B86" s="18"/>
       <c r="C86" s="17"/>
       <c r="D86" s="19"/>
-      <c r="E86" s="18"/>
-      <c r="F86" s="18"/>
-      <c r="G86" s="18"/>
-      <c r="H86" s="18"/>
-      <c r="I86" s="18"/>
-      <c r="J86" s="18"/>
-      <c r="K86" s="18"/>
-      <c r="L86" s="18"/>
-      <c r="M86" s="18"/>
-      <c r="N86" s="18"/>
-      <c r="O86" s="18"/>
-      <c r="P86" s="18"/>
-      <c r="Q86" s="18"/>
-      <c r="R86" s="18"/>
-      <c r="S86" s="18"/>
-      <c r="T86" s="18"/>
-      <c r="U86" s="18"/>
-      <c r="V86" s="18"/>
-      <c r="W86" s="18"/>
-      <c r="X86" s="18"/>
-      <c r="Y86" s="18"/>
-      <c r="Z86" s="18"/>
-      <c r="AA86" s="18"/>
-      <c r="AB86" s="18"/>
-      <c r="AC86" s="18"/>
-      <c r="AD86" s="18"/>
-      <c r="AE86" s="18"/>
-      <c r="AF86" s="18"/>
-      <c r="AG86" s="18"/>
-      <c r="AH86" s="18"/>
+      <c r="E86" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F86" s="21"/>
+      <c r="G86" s="22"/>
+      <c r="H86" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="I86" s="21"/>
+      <c r="J86" s="21"/>
+      <c r="K86" s="21"/>
+      <c r="L86" s="22"/>
+      <c r="M86" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="N86" s="21"/>
+      <c r="O86" s="21"/>
+      <c r="P86" s="21"/>
+      <c r="Q86" s="21"/>
+      <c r="R86" s="21"/>
+      <c r="S86" s="21"/>
+      <c r="T86" s="21"/>
+      <c r="U86" s="21"/>
+      <c r="V86" s="21"/>
+      <c r="W86" s="21"/>
+      <c r="X86" s="21"/>
+      <c r="Y86" s="21"/>
+      <c r="Z86" s="21"/>
+      <c r="AA86" s="21"/>
+      <c r="AB86" s="21"/>
+      <c r="AC86" s="21"/>
+      <c r="AD86" s="21"/>
+      <c r="AE86" s="21"/>
+      <c r="AF86" s="21"/>
+      <c r="AG86" s="21"/>
+      <c r="AH86" s="22"/>
       <c r="AI86" s="18"/>
     </row>
     <row r="87" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -12209,42 +12614,42 @@
       <c r="B87" s="18"/>
       <c r="C87" s="17"/>
       <c r="D87" s="19"/>
-      <c r="E87" s="20" t="s">
-        <v>24</v>
+      <c r="E87" s="35" t="s">
+        <v>27</v>
       </c>
-      <c r="F87" s="21"/>
-      <c r="G87" s="22"/>
-      <c r="H87" s="20" t="s">
-        <v>25</v>
+      <c r="F87" s="36"/>
+      <c r="G87" s="37"/>
+      <c r="H87" s="44" t="s">
+        <v>32</v>
       </c>
-      <c r="I87" s="21"/>
-      <c r="J87" s="21"/>
-      <c r="K87" s="21"/>
-      <c r="L87" s="22"/>
-      <c r="M87" s="20" t="s">
-        <v>26</v>
+      <c r="I87" s="36"/>
+      <c r="J87" s="36"/>
+      <c r="K87" s="36"/>
+      <c r="L87" s="37"/>
+      <c r="M87" s="23" t="s">
+        <v>33</v>
       </c>
-      <c r="N87" s="21"/>
-      <c r="O87" s="21"/>
-      <c r="P87" s="21"/>
-      <c r="Q87" s="21"/>
-      <c r="R87" s="21"/>
-      <c r="S87" s="21"/>
-      <c r="T87" s="21"/>
-      <c r="U87" s="21"/>
-      <c r="V87" s="21"/>
-      <c r="W87" s="21"/>
-      <c r="X87" s="21"/>
-      <c r="Y87" s="21"/>
-      <c r="Z87" s="21"/>
-      <c r="AA87" s="21"/>
-      <c r="AB87" s="21"/>
-      <c r="AC87" s="21"/>
-      <c r="AD87" s="21"/>
-      <c r="AE87" s="21"/>
-      <c r="AF87" s="21"/>
-      <c r="AG87" s="21"/>
-      <c r="AH87" s="22"/>
+      <c r="N87" s="24"/>
+      <c r="O87" s="24"/>
+      <c r="P87" s="24"/>
+      <c r="Q87" s="24"/>
+      <c r="R87" s="24"/>
+      <c r="S87" s="24"/>
+      <c r="T87" s="24"/>
+      <c r="U87" s="24"/>
+      <c r="V87" s="24"/>
+      <c r="W87" s="24"/>
+      <c r="X87" s="24"/>
+      <c r="Y87" s="24"/>
+      <c r="Z87" s="24"/>
+      <c r="AA87" s="24"/>
+      <c r="AB87" s="24"/>
+      <c r="AC87" s="24"/>
+      <c r="AD87" s="24"/>
+      <c r="AE87" s="24"/>
+      <c r="AF87" s="24"/>
+      <c r="AG87" s="24"/>
+      <c r="AH87" s="25"/>
       <c r="AI87" s="18"/>
     </row>
     <row r="88" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -12252,42 +12657,38 @@
       <c r="B88" s="18"/>
       <c r="C88" s="17"/>
       <c r="D88" s="19"/>
-      <c r="E88" s="54" t="s">
-        <v>27</v>
+      <c r="E88" s="38"/>
+      <c r="F88" s="45"/>
+      <c r="G88" s="40"/>
+      <c r="H88" s="38"/>
+      <c r="I88" s="45"/>
+      <c r="J88" s="45"/>
+      <c r="K88" s="45"/>
+      <c r="L88" s="40"/>
+      <c r="M88" s="26" t="s">
+        <v>34</v>
       </c>
-      <c r="F88" s="55"/>
-      <c r="G88" s="56"/>
-      <c r="H88" s="63" t="s">
-        <v>32</v>
-      </c>
-      <c r="I88" s="55"/>
-      <c r="J88" s="55"/>
-      <c r="K88" s="55"/>
-      <c r="L88" s="56"/>
-      <c r="M88" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="N88" s="24"/>
-      <c r="O88" s="24"/>
-      <c r="P88" s="24"/>
-      <c r="Q88" s="24"/>
-      <c r="R88" s="24"/>
-      <c r="S88" s="24"/>
-      <c r="T88" s="24"/>
-      <c r="U88" s="24"/>
-      <c r="V88" s="24"/>
-      <c r="W88" s="24"/>
-      <c r="X88" s="24"/>
-      <c r="Y88" s="24"/>
-      <c r="Z88" s="24"/>
-      <c r="AA88" s="24"/>
-      <c r="AB88" s="24"/>
-      <c r="AC88" s="24"/>
-      <c r="AD88" s="24"/>
-      <c r="AE88" s="24"/>
-      <c r="AF88" s="24"/>
-      <c r="AG88" s="24"/>
-      <c r="AH88" s="25"/>
+      <c r="N88" s="18"/>
+      <c r="O88" s="18"/>
+      <c r="P88" s="18"/>
+      <c r="Q88" s="18"/>
+      <c r="R88" s="18"/>
+      <c r="S88" s="18"/>
+      <c r="T88" s="18"/>
+      <c r="U88" s="18"/>
+      <c r="V88" s="18"/>
+      <c r="W88" s="18"/>
+      <c r="X88" s="18"/>
+      <c r="Y88" s="18"/>
+      <c r="Z88" s="18"/>
+      <c r="AA88" s="18"/>
+      <c r="AB88" s="18"/>
+      <c r="AC88" s="18"/>
+      <c r="AD88" s="18"/>
+      <c r="AE88" s="18"/>
+      <c r="AF88" s="18"/>
+      <c r="AG88" s="18"/>
+      <c r="AH88" s="27"/>
       <c r="AI88" s="18"/>
     </row>
     <row r="89" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -12295,16 +12696,16 @@
       <c r="B89" s="18"/>
       <c r="C89" s="17"/>
       <c r="D89" s="19"/>
-      <c r="E89" s="57"/>
-      <c r="F89" s="64"/>
-      <c r="G89" s="59"/>
-      <c r="H89" s="57"/>
-      <c r="I89" s="64"/>
-      <c r="J89" s="64"/>
-      <c r="K89" s="64"/>
-      <c r="L89" s="59"/>
+      <c r="E89" s="31"/>
+      <c r="F89" s="32"/>
+      <c r="G89" s="33"/>
+      <c r="H89" s="31"/>
+      <c r="I89" s="32"/>
+      <c r="J89" s="32"/>
+      <c r="K89" s="32"/>
+      <c r="L89" s="33"/>
       <c r="M89" s="26" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="N89" s="18"/>
       <c r="O89" s="18"/>
@@ -12334,38 +12735,42 @@
       <c r="B90" s="18"/>
       <c r="C90" s="17"/>
       <c r="D90" s="19"/>
-      <c r="E90" s="31"/>
-      <c r="F90" s="32"/>
-      <c r="G90" s="33"/>
-      <c r="H90" s="31"/>
-      <c r="I90" s="32"/>
-      <c r="J90" s="32"/>
-      <c r="K90" s="32"/>
-      <c r="L90" s="33"/>
-      <c r="M90" s="26" t="s">
-        <v>39</v>
+      <c r="E90" s="35" t="s">
+        <v>28</v>
       </c>
-      <c r="N90" s="18"/>
-      <c r="O90" s="18"/>
-      <c r="P90" s="18"/>
-      <c r="Q90" s="18"/>
-      <c r="R90" s="18"/>
-      <c r="S90" s="18"/>
-      <c r="T90" s="18"/>
-      <c r="U90" s="18"/>
-      <c r="V90" s="18"/>
-      <c r="W90" s="18"/>
-      <c r="X90" s="18"/>
-      <c r="Y90" s="18"/>
-      <c r="Z90" s="18"/>
-      <c r="AA90" s="18"/>
-      <c r="AB90" s="18"/>
-      <c r="AC90" s="18"/>
-      <c r="AD90" s="18"/>
-      <c r="AE90" s="18"/>
-      <c r="AF90" s="18"/>
-      <c r="AG90" s="18"/>
-      <c r="AH90" s="27"/>
+      <c r="F90" s="36"/>
+      <c r="G90" s="37"/>
+      <c r="H90" s="35" t="s">
+        <v>29</v>
+      </c>
+      <c r="I90" s="36"/>
+      <c r="J90" s="36"/>
+      <c r="K90" s="36"/>
+      <c r="L90" s="37"/>
+      <c r="M90" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="N90" s="24"/>
+      <c r="O90" s="24"/>
+      <c r="P90" s="24"/>
+      <c r="Q90" s="24"/>
+      <c r="R90" s="24"/>
+      <c r="S90" s="24"/>
+      <c r="T90" s="24"/>
+      <c r="U90" s="24"/>
+      <c r="V90" s="24"/>
+      <c r="W90" s="24"/>
+      <c r="X90" s="24"/>
+      <c r="Y90" s="24"/>
+      <c r="Z90" s="24"/>
+      <c r="AA90" s="24"/>
+      <c r="AB90" s="24"/>
+      <c r="AC90" s="24"/>
+      <c r="AD90" s="24"/>
+      <c r="AE90" s="24"/>
+      <c r="AF90" s="24"/>
+      <c r="AG90" s="24"/>
+      <c r="AH90" s="25"/>
       <c r="AI90" s="18"/>
     </row>
     <row r="91" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -12373,42 +12778,36 @@
       <c r="B91" s="18"/>
       <c r="C91" s="17"/>
       <c r="D91" s="19"/>
-      <c r="E91" s="54" t="s">
-        <v>28</v>
-      </c>
-      <c r="F91" s="55"/>
-      <c r="G91" s="56"/>
-      <c r="H91" s="54" t="s">
-        <v>29</v>
-      </c>
-      <c r="I91" s="55"/>
-      <c r="J91" s="55"/>
-      <c r="K91" s="55"/>
-      <c r="L91" s="56"/>
-      <c r="M91" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="N91" s="24"/>
-      <c r="O91" s="24"/>
-      <c r="P91" s="24"/>
-      <c r="Q91" s="24"/>
-      <c r="R91" s="24"/>
-      <c r="S91" s="24"/>
-      <c r="T91" s="24"/>
-      <c r="U91" s="24"/>
-      <c r="V91" s="24"/>
-      <c r="W91" s="24"/>
-      <c r="X91" s="24"/>
-      <c r="Y91" s="24"/>
-      <c r="Z91" s="24"/>
-      <c r="AA91" s="24"/>
-      <c r="AB91" s="24"/>
-      <c r="AC91" s="24"/>
-      <c r="AD91" s="24"/>
-      <c r="AE91" s="24"/>
-      <c r="AF91" s="24"/>
-      <c r="AG91" s="24"/>
-      <c r="AH91" s="25"/>
+      <c r="E91" s="41"/>
+      <c r="F91" s="42"/>
+      <c r="G91" s="43"/>
+      <c r="H91" s="41"/>
+      <c r="I91" s="42"/>
+      <c r="J91" s="42"/>
+      <c r="K91" s="42"/>
+      <c r="L91" s="43"/>
+      <c r="M91" s="28"/>
+      <c r="N91" s="29"/>
+      <c r="O91" s="29"/>
+      <c r="P91" s="29"/>
+      <c r="Q91" s="29"/>
+      <c r="R91" s="29"/>
+      <c r="S91" s="29"/>
+      <c r="T91" s="29"/>
+      <c r="U91" s="29"/>
+      <c r="V91" s="29"/>
+      <c r="W91" s="29"/>
+      <c r="X91" s="29"/>
+      <c r="Y91" s="29"/>
+      <c r="Z91" s="29"/>
+      <c r="AA91" s="29"/>
+      <c r="AB91" s="29"/>
+      <c r="AC91" s="29"/>
+      <c r="AD91" s="29"/>
+      <c r="AE91" s="29"/>
+      <c r="AF91" s="29"/>
+      <c r="AG91" s="29"/>
+      <c r="AH91" s="30"/>
       <c r="AI91" s="18"/>
     </row>
     <row r="92" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -12416,36 +12815,42 @@
       <c r="B92" s="18"/>
       <c r="C92" s="17"/>
       <c r="D92" s="19"/>
-      <c r="E92" s="60"/>
-      <c r="F92" s="61"/>
-      <c r="G92" s="62"/>
-      <c r="H92" s="60"/>
-      <c r="I92" s="61"/>
-      <c r="J92" s="61"/>
-      <c r="K92" s="61"/>
-      <c r="L92" s="62"/>
-      <c r="M92" s="28"/>
-      <c r="N92" s="29"/>
-      <c r="O92" s="29"/>
-      <c r="P92" s="29"/>
-      <c r="Q92" s="29"/>
-      <c r="R92" s="29"/>
-      <c r="S92" s="29"/>
-      <c r="T92" s="29"/>
-      <c r="U92" s="29"/>
-      <c r="V92" s="29"/>
-      <c r="W92" s="29"/>
-      <c r="X92" s="29"/>
-      <c r="Y92" s="29"/>
-      <c r="Z92" s="29"/>
-      <c r="AA92" s="29"/>
-      <c r="AB92" s="29"/>
-      <c r="AC92" s="29"/>
-      <c r="AD92" s="29"/>
-      <c r="AE92" s="29"/>
-      <c r="AF92" s="29"/>
-      <c r="AG92" s="29"/>
-      <c r="AH92" s="30"/>
+      <c r="E92" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="F92" s="36"/>
+      <c r="G92" s="37"/>
+      <c r="H92" s="35" t="s">
+        <v>37</v>
+      </c>
+      <c r="I92" s="36"/>
+      <c r="J92" s="36"/>
+      <c r="K92" s="36"/>
+      <c r="L92" s="37"/>
+      <c r="M92" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="N92" s="24"/>
+      <c r="O92" s="24"/>
+      <c r="P92" s="24"/>
+      <c r="Q92" s="24"/>
+      <c r="R92" s="24"/>
+      <c r="S92" s="24"/>
+      <c r="T92" s="24"/>
+      <c r="U92" s="24"/>
+      <c r="V92" s="24"/>
+      <c r="W92" s="24"/>
+      <c r="X92" s="24"/>
+      <c r="Y92" s="24"/>
+      <c r="Z92" s="24"/>
+      <c r="AA92" s="24"/>
+      <c r="AB92" s="24"/>
+      <c r="AC92" s="24"/>
+      <c r="AD92" s="24"/>
+      <c r="AE92" s="24"/>
+      <c r="AF92" s="24"/>
+      <c r="AG92" s="24"/>
+      <c r="AH92" s="25"/>
       <c r="AI92" s="18"/>
     </row>
     <row r="93" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -12453,117 +12858,75 @@
       <c r="B93" s="18"/>
       <c r="C93" s="17"/>
       <c r="D93" s="19"/>
-      <c r="E93" s="54" t="s">
-        <v>36</v>
+      <c r="E93" s="38"/>
+      <c r="F93" s="39"/>
+      <c r="G93" s="40"/>
+      <c r="H93" s="38"/>
+      <c r="I93" s="39"/>
+      <c r="J93" s="39"/>
+      <c r="K93" s="39"/>
+      <c r="L93" s="40"/>
+      <c r="M93" s="26" t="s">
+        <v>44</v>
       </c>
-      <c r="F93" s="55"/>
-      <c r="G93" s="56"/>
-      <c r="H93" s="54" t="s">
-        <v>37</v>
-      </c>
-      <c r="I93" s="55"/>
-      <c r="J93" s="55"/>
-      <c r="K93" s="55"/>
-      <c r="L93" s="56"/>
-      <c r="M93" s="23" t="s">
-        <v>43</v>
-      </c>
-      <c r="N93" s="24"/>
-      <c r="O93" s="24"/>
-      <c r="P93" s="24"/>
-      <c r="Q93" s="24"/>
-      <c r="R93" s="24"/>
-      <c r="S93" s="24"/>
-      <c r="T93" s="24"/>
-      <c r="U93" s="24"/>
-      <c r="V93" s="24"/>
-      <c r="W93" s="24"/>
-      <c r="X93" s="24"/>
-      <c r="Y93" s="24"/>
-      <c r="Z93" s="24"/>
-      <c r="AA93" s="24"/>
-      <c r="AB93" s="24"/>
-      <c r="AC93" s="24"/>
-      <c r="AD93" s="24"/>
-      <c r="AE93" s="24"/>
-      <c r="AF93" s="24"/>
-      <c r="AG93" s="24"/>
-      <c r="AH93" s="25"/>
+      <c r="N93" s="34"/>
+      <c r="O93" s="34"/>
+      <c r="P93" s="34"/>
+      <c r="Q93" s="34"/>
+      <c r="R93" s="34"/>
+      <c r="S93" s="34"/>
+      <c r="T93" s="34"/>
+      <c r="U93" s="34"/>
+      <c r="V93" s="34"/>
+      <c r="W93" s="34"/>
+      <c r="X93" s="34"/>
+      <c r="Y93" s="34"/>
+      <c r="Z93" s="34"/>
+      <c r="AA93" s="34"/>
+      <c r="AB93" s="34"/>
+      <c r="AC93" s="34"/>
+      <c r="AD93" s="34"/>
+      <c r="AE93" s="34"/>
+      <c r="AF93" s="34"/>
+      <c r="AG93" s="34"/>
+      <c r="AH93" s="27"/>
       <c r="AI93" s="18"/>
     </row>
     <row r="94" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A94" s="18"/>
-      <c r="B94" s="18"/>
-      <c r="C94" s="17"/>
-      <c r="D94" s="19"/>
-      <c r="E94" s="57"/>
-      <c r="F94" s="58"/>
-      <c r="G94" s="59"/>
-      <c r="H94" s="57"/>
-      <c r="I94" s="58"/>
-      <c r="J94" s="58"/>
-      <c r="K94" s="58"/>
-      <c r="L94" s="59"/>
-      <c r="M94" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="N94" s="34"/>
-      <c r="O94" s="34"/>
-      <c r="P94" s="34"/>
-      <c r="Q94" s="34"/>
-      <c r="R94" s="34"/>
-      <c r="S94" s="34"/>
-      <c r="T94" s="34"/>
-      <c r="U94" s="34"/>
-      <c r="V94" s="34"/>
-      <c r="W94" s="34"/>
-      <c r="X94" s="34"/>
-      <c r="Y94" s="34"/>
-      <c r="Z94" s="34"/>
-      <c r="AA94" s="34"/>
-      <c r="AB94" s="34"/>
-      <c r="AC94" s="34"/>
-      <c r="AD94" s="34"/>
-      <c r="AE94" s="34"/>
-      <c r="AF94" s="34"/>
-      <c r="AG94" s="34"/>
-      <c r="AH94" s="27"/>
-      <c r="AI94" s="18"/>
-    </row>
-    <row r="95" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="E95" s="60"/>
-      <c r="F95" s="61"/>
-      <c r="G95" s="62"/>
-      <c r="H95" s="60"/>
-      <c r="I95" s="61"/>
-      <c r="J95" s="61"/>
-      <c r="K95" s="61"/>
-      <c r="L95" s="62"/>
-      <c r="M95" s="28" t="s">
+      <c r="E94" s="41"/>
+      <c r="F94" s="42"/>
+      <c r="G94" s="43"/>
+      <c r="H94" s="41"/>
+      <c r="I94" s="42"/>
+      <c r="J94" s="42"/>
+      <c r="K94" s="42"/>
+      <c r="L94" s="43"/>
+      <c r="M94" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="N95" s="29"/>
-      <c r="O95" s="29"/>
-      <c r="P95" s="29"/>
-      <c r="Q95" s="29"/>
-      <c r="R95" s="29"/>
-      <c r="S95" s="29"/>
-      <c r="T95" s="29"/>
-      <c r="U95" s="29"/>
-      <c r="V95" s="29"/>
-      <c r="W95" s="29"/>
-      <c r="X95" s="29"/>
-      <c r="Y95" s="29"/>
-      <c r="Z95" s="29"/>
-      <c r="AA95" s="29"/>
-      <c r="AB95" s="29"/>
-      <c r="AC95" s="29"/>
-      <c r="AD95" s="29"/>
-      <c r="AE95" s="29"/>
-      <c r="AF95" s="29"/>
-      <c r="AG95" s="29"/>
-      <c r="AH95" s="30"/>
+      <c r="N94" s="29"/>
+      <c r="O94" s="29"/>
+      <c r="P94" s="29"/>
+      <c r="Q94" s="29"/>
+      <c r="R94" s="29"/>
+      <c r="S94" s="29"/>
+      <c r="T94" s="29"/>
+      <c r="U94" s="29"/>
+      <c r="V94" s="29"/>
+      <c r="W94" s="29"/>
+      <c r="X94" s="29"/>
+      <c r="Y94" s="29"/>
+      <c r="Z94" s="29"/>
+      <c r="AA94" s="29"/>
+      <c r="AB94" s="29"/>
+      <c r="AC94" s="29"/>
+      <c r="AD94" s="29"/>
+      <c r="AE94" s="29"/>
+      <c r="AF94" s="29"/>
+      <c r="AG94" s="29"/>
+      <c r="AH94" s="30"/>
     </row>
+    <row r="95" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="96" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="97" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="98" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -12893,15 +13256,8 @@
     <row r="422" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="423" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="424" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="425" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="E93:G95"/>
-    <mergeCell ref="H93:L95"/>
-    <mergeCell ref="E91:G92"/>
-    <mergeCell ref="H88:L89"/>
-    <mergeCell ref="H91:L92"/>
-    <mergeCell ref="E88:G89"/>
     <mergeCell ref="AF3:AI3"/>
     <mergeCell ref="E1:O1"/>
     <mergeCell ref="R1:X1"/>
@@ -12913,16 +13269,22 @@
     <mergeCell ref="AF2:AI2"/>
     <mergeCell ref="E3:O3"/>
     <mergeCell ref="AA3:AE3"/>
+    <mergeCell ref="E92:G94"/>
+    <mergeCell ref="H92:L94"/>
+    <mergeCell ref="E90:G91"/>
+    <mergeCell ref="H87:L88"/>
+    <mergeCell ref="H90:L91"/>
+    <mergeCell ref="E87:G88"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <hyperlinks>
-    <hyperlink ref="D79" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="D78" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId2"/>
   <rowBreaks count="2" manualBreakCount="2">
-    <brk id="46" max="34" man="1"/>
-    <brk id="80" max="34" man="1"/>
+    <brk id="45" max="34" man="1"/>
+    <brk id="79" max="34" man="1"/>
   </rowBreaks>
   <drawing r:id="rId3"/>
 </worksheet>
